--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104730_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104730_W31.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.125</v>
+        <v>5.9124</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2827</v>
+        <v>3.867</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8423</v>
+        <v>2.0454</v>
       </c>
       <c r="G2" t="n">
-        <v>0.172</v>
+        <v>0.1747</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5936</v>
+        <v>-0.5893</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.764</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7402</v>
+        <v>0.7348</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0752</v>
+        <v>0.0722</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6651</v>
+        <v>0.6626</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5682</v>
+        <v>-0.5601</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6688</v>
+        <v>-0.6615</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1005</v>
+        <v>0.1014</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.794</v>
+        <v>0.5783</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8143</v>
+        <v>0.4085</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0203</v>
+        <v>0.1699</v>
       </c>
       <c r="V2" t="n">
-        <v>3.1143</v>
+        <v>3.1107</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5614</v>
+        <v>5.9096</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8092</v>
+        <v>6.8976</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7522</v>
+        <v>-0.988</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6787</v>
+        <v>5.5305</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0218</v>
+        <v>2.1998</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6569</v>
+        <v>3.3307</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2609</v>
+        <v>7.2787</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5328</v>
+        <v>3.0337</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7281</v>
+        <v>4.245</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-1.7481</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.511</v>
+        <v>-0.8339</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0712</v>
+        <v>-0.9143</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4991</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2719</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2082</v>
+        <v>0.0117</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.044</v>
+        <v>-0.1048</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1642</v>
+        <v>0.1165</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3181</v>
+        <v>-0.3155</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2268</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0509</v>
+        <v>5.8222</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1868</v>
+        <v>3.737</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1359</v>
+        <v>2.0852</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5326</v>
+        <v>4.6753</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1999</v>
+        <v>1.0198</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3327</v>
+        <v>3.6556</v>
       </c>
       <c r="J4" t="n">
-        <v>7.2916</v>
+        <v>5.247</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0415</v>
+        <v>1.5233</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2501</v>
+        <v>3.7237</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.759</v>
+        <v>-0.5717</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8416</v>
+        <v>-0.5036</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9174</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6816</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3631</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0447</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8444</v>
+        <v>0.0558</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8329</v>
+        <v>-0.0955</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0115</v>
+        <v>0.1513</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3188</v>
+        <v>1.3187</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4101</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9278</v>
+        <v>4.8049</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1262</v>
+        <v>2.7624</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8016</v>
+        <v>2.0425</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2133</v>
+        <v>1.2111</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.62</v>
+        <v>-2.6116</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8333</v>
+        <v>3.8227</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7139</v>
+        <v>1.6999</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3877</v>
+        <v>-1.3897</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1016</v>
+        <v>3.0896</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5006</v>
+        <v>-0.4888</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2323</v>
+        <v>-1.2219</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7317</v>
+        <v>0.7331</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.763</v>
+        <v>0.1173</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1799</v>
+        <v>-0.523</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4169</v>
+        <v>0.6404</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5687</v>
+        <v>2.5659</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4489</v>
+        <v>2.5887</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5546</v>
+        <v>1.4206</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8943</v>
+        <v>1.1681</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2761</v>
+        <v>2.2773</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6605</v>
+        <v>-0.6555</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9366</v>
+        <v>2.9327</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7127</v>
+        <v>1.7042</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1961</v>
+        <v>0.1929</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5165</v>
+        <v>1.5114</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5634</v>
+        <v>0.573</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8566</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.4214</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5825</v>
+        <v>0.718</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1134</v>
+        <v>-0.2349</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6959</v>
+        <v>0.9529</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. QUINTELA</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9063</v>
+        <v>2.3926</v>
       </c>
       <c r="E7" t="n">
-        <v>1.569</v>
+        <v>1.4219</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3373</v>
+        <v>0.9707</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9922</v>
+        <v>2.0918</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7972</v>
+        <v>0.4906</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1951</v>
+        <v>1.6012</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8495</v>
+        <v>3.3385</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8122</v>
+        <v>1.8271</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>1.5114</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1427</v>
+        <v>-1.2467</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.015</v>
+        <v>-1.3365</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1578</v>
+        <v>0.0898</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2272</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2272</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8463000000000001</v>
+        <v>-0.1544</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7195</v>
+        <v>-0.5508</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1268</v>
+        <v>0.3964</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>E. QUINTELA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.893</v>
+        <v>1.5775</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2663</v>
+        <v>1.3304</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6267</v>
+        <v>0.2471</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5846</v>
+        <v>0.9909</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1052</v>
+        <v>0.7957</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4793</v>
+        <v>0.1952</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8474</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4735</v>
+        <v>0.8101</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3355</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2244</v>
+        <v>0.1435</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3682</v>
+        <v>-0.0144</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1438</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9087</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3631</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2719</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.5168</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.044</v>
+        <v>0.483</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6705</v>
+        <v>0.0338</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2268</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8643999999999999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0913</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8091</v>
+        <v>1.3256</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0135</v>
+        <v>-0.0417</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7955</v>
+        <v>1.3673</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0899</v>
+        <v>0.5825</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4868</v>
+        <v>0.1011</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6031</v>
+        <v>0.4815</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3484</v>
+        <v>0.7963</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8318</v>
+        <v>0.4612</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5165</v>
+        <v>0.3351</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2584</v>
+        <v>-0.2138</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.345</v>
+        <v>-0.3601</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0866</v>
+        <v>0.1463</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4544</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8175</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7352</v>
+        <v>0.0618</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9717</v>
+        <v>-0.3324</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2365</v>
+        <v>0.3942</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1351</v>
+        <v>1.0512</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6014</v>
+        <v>0.5351</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5336</v>
+        <v>0.5161</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5409</v>
+        <v>1.5378</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8791</v>
+        <v>-0.8763</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4199</v>
+        <v>2.414</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8669</v>
+        <v>2.8558</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0977</v>
+        <v>-0.1002</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9645</v>
+        <v>2.9559</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.326</v>
+        <v>-1.318</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7814</v>
+        <v>-0.7761</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5446</v>
+        <v>-0.5419</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2758</v>
+        <v>0.1963</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2336</v>
+        <v>0.1833</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0421</v>
+        <v>0.013</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4684</v>
+        <v>0.106</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1171</v>
+        <v>-2.1829</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5855</v>
+        <v>2.2889</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1202</v>
+        <v>0.1185</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1488</v>
+        <v>0.1467</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0286</v>
+        <v>-0.0283</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.5062</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1181</v>
+        <v>1.1097</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6025</v>
+        <v>-0.6035</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3954</v>
+        <v>-0.3877</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.9629</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5739</v>
+        <v>0.5752</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8708</v>
+        <v>0.5111</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0254</v>
+        <v>-0.0258</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8454</v>
+        <v>0.5369</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.9835</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0272</v>
+        <v>-0.2684</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.7151</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4326</v>
+        <v>-0.4331</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5012</v>
+        <v>-0.4999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0668</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4587</v>
+        <v>0.4564</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4414</v>
+        <v>0.4392</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8913</v>
+        <v>-0.8895</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5184</v>
+        <v>-0.5171</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3728</v>
+        <v>-0.3724</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6917</v>
+        <v>0.5179</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6501</v>
+        <v>0.4133</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0416</v>
+        <v>0.1046</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.833</v>
+        <v>-2.1218</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2185</v>
+        <v>-2.928</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3854</v>
+        <v>0.8062</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8698</v>
+        <v>-0.8688</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8205</v>
+        <v>-0.8162</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0493</v>
+        <v>-0.0526</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1137</v>
+        <v>-0.1219</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3517</v>
+        <v>0.348</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4654</v>
+        <v>-0.4698</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7561</v>
+        <v>-0.7469</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1722</v>
+        <v>-1.1642</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4161</v>
+        <v>0.4173</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0545</v>
+        <v>-0.3425</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8329</v>
+        <v>-0.5298</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2216</v>
+        <v>0.1873</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>27.6839</v>
+        <v>28.3854</v>
       </c>
       <c r="E14" t="n">
-        <v>16.0469</v>
+        <v>16.551</v>
       </c>
       <c r="F14" t="n">
-        <v>11.6367</v>
+        <v>11.8344</v>
       </c>
       <c r="G14" t="n">
-        <v>17.8981</v>
+        <v>17.8885</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3152</v>
+        <v>-1.2951</v>
       </c>
       <c r="I14" t="n">
-        <v>19.2132</v>
+        <v>19.1835</v>
       </c>
       <c r="J14" t="n">
-        <v>25.4537</v>
+        <v>25.3433</v>
       </c>
       <c r="K14" t="n">
-        <v>7.9648</v>
+        <v>7.905500000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>17.4887</v>
+        <v>17.4378</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.555500000000001</v>
+        <v>-7.4548</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.2798</v>
+        <v>-9.2005</v>
       </c>
       <c r="O14" t="n">
-        <v>1.7244</v>
+        <v>1.7457</v>
       </c>
       <c r="P14" t="n">
-        <v>2.272000000000001</v>
+        <v>2.276400000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.039</v>
+        <v>-17.0724</v>
       </c>
       <c r="R14" t="n">
-        <v>19.311</v>
+        <v>19.3488</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0823</v>
+        <v>2.7881</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5759</v>
+        <v>-0.9089000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6581</v>
+        <v>3.6972</v>
       </c>
       <c r="V14" t="n">
-        <v>5.4316</v>
+        <v>5.432500000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>9.208299999999999</v>
+        <v>9.1892</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.776699999999999</v>
+        <v>-3.756699999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5326</v>
+        <v>3.5868</v>
       </c>
       <c r="E15" t="n">
-        <v>4.207</v>
+        <v>3.246</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3256</v>
+        <v>0.3409</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1518</v>
+        <v>2.1515</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9182</v>
+        <v>0.9164</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2336</v>
+        <v>1.2352</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0044</v>
+        <v>2.9958</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6996</v>
+        <v>1.6925</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3048</v>
+        <v>1.3033</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8527</v>
+        <v>-0.8442</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7814</v>
+        <v>-0.7761</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0712</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8583</v>
+        <v>-0.0882</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8837</v>
+        <v>-0.0653</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0254</v>
+        <v>-0.0229</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3188</v>
+        <v>0.3155</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6924</v>
+        <v>2.3788</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3459</v>
+        <v>3.2045</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6535</v>
+        <v>-0.8257</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8839</v>
+        <v>1.8794</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1347</v>
+        <v>4.1252</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.2508</v>
+        <v>-2.2458</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4128</v>
+        <v>4.3987</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4128</v>
+        <v>4.3987</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5289</v>
+        <v>-2.5193</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.278</v>
+        <v>-0.2734</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2508</v>
+        <v>-2.2458</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.626</v>
+        <v>0.3205</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1138</v>
+        <v>-0.0073</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5122</v>
+        <v>0.3278</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1199</v>
+        <v>0.3468</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0536</v>
+        <v>1.3238</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9338</v>
+        <v>-0.977</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1903</v>
+        <v>0.1858</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4472</v>
+        <v>2.4392</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2568</v>
+        <v>-2.2535</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3575</v>
+        <v>1.343</v>
       </c>
       <c r="K17" t="n">
-        <v>2.898</v>
+        <v>2.8851</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.5405</v>
+        <v>-1.542</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1672</v>
+        <v>-1.1573</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4508</v>
+        <v>-0.4458</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7163</v>
+        <v>-0.7114</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8167</v>
+        <v>0.0441</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5367</v>
+        <v>-0.1769</v>
       </c>
       <c r="U17" t="n">
-        <v>0.28</v>
+        <v>0.2211</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4775</v>
+        <v>-1.4764</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6078</v>
+        <v>-0.4954</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3634</v>
+        <v>-1.1388</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7556</v>
+        <v>0.6434</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4895</v>
+        <v>-1.4874</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2141</v>
+        <v>0.2152</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7036</v>
+        <v>-1.7026</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7825</v>
+        <v>-0.7879</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1616</v>
+        <v>0.1584</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.944</v>
+        <v>-0.9463</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.707</v>
+        <v>-0.6995</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0526</v>
+        <v>0.0568</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7563</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0176</v>
+        <v>0.1301</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5363</v>
+        <v>-0.3022</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.4324</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8143</v>
+        <v>-2.1204</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4976</v>
+        <v>-0.0418</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3167</v>
+        <v>-2.0786</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9967</v>
+        <v>-2.9957</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2247</v>
+        <v>1.221</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.2214</v>
+        <v>-4.2167</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1805</v>
+        <v>-0.1911</v>
       </c>
       <c r="K19" t="n">
-        <v>1.36</v>
+        <v>1.351</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5405</v>
+        <v>-1.542</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8162</v>
+        <v>-2.8047</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1353</v>
+        <v>-0.13</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.6809</v>
+        <v>-2.6747</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2488</v>
+        <v>-0.5587</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0221</v>
+        <v>-0.5532</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2267</v>
+        <v>-0.0055</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W19" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9046</v>
+        <v>-2.5455</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7113</v>
+        <v>-0.4849</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1933</v>
+        <v>-2.0606</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9105</v>
+        <v>-1.9088</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7348</v>
+        <v>-0.7351</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1757</v>
+        <v>-1.1736</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2013</v>
+        <v>-0.2036</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2013</v>
+        <v>-0.2036</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7092</v>
+        <v>-1.7052</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5335</v>
+        <v>-0.5315</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1757</v>
+        <v>-1.1736</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6992</v>
+        <v>-0.3393</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6247</v>
+        <v>-0.3904</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0745</v>
+        <v>0.0512</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8276</v>
+        <v>-3.5649</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4</v>
+        <v>-2.4163</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4276</v>
+        <v>-1.1486</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.2123</v>
+        <v>-4.4429</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4981</v>
+        <v>-2.5618</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.7142</v>
+        <v>-1.8811</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.009</v>
+        <v>-1.863</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4312</v>
+        <v>-1.1106</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5778</v>
+        <v>-0.7524</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.2033</v>
+        <v>-2.5799</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0669</v>
+        <v>-1.4511</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1363</v>
+        <v>-1.1287</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9985000000000001</v>
+        <v>-0.1024</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7449</v>
+        <v>-0.5532</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2536</v>
+        <v>0.4509</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3862</v>
+        <v>-0.1578</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3862</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>O. PAULI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0446</v>
+        <v>-3.8456</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8789</v>
+        <v>-1.7834</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1656</v>
+        <v>-2.0622</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.4469</v>
+        <v>-1.4805</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5628</v>
+        <v>0.3531</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.884</v>
+        <v>-1.8336</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8568</v>
+        <v>2.344</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1052</v>
+        <v>1.5029</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7516</v>
+        <v>0.8411</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5901</v>
+        <v>-3.8244</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4577</v>
+        <v>-1.1497</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1324</v>
+        <v>-2.6747</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1359</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1359</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5742</v>
+        <v>-0.928</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0221</v>
+        <v>-0.6415</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4479</v>
+        <v>-0.2865</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1594</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. PAULI</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3443</v>
+        <v>-3.9496</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2307</v>
+        <v>-2.3983</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1135</v>
+        <v>-1.5513</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4831</v>
+        <v>-3.4918</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3524</v>
+        <v>-1.4707</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8354</v>
+        <v>-2.0211</v>
       </c>
       <c r="J23" t="n">
-        <v>2.355</v>
+        <v>-0.916</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5095</v>
+        <v>-1.3552</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8455</v>
+        <v>0.4392</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.838</v>
+        <v>-2.5758</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1571</v>
+        <v>-0.1155</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.6809</v>
+        <v>-2.4603</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3631</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4078</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4307</v>
+        <v>-0.2788</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1105</v>
+        <v>-0.3441</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3202</v>
+        <v>0.0653</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.0674</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0674</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>A. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8062</v>
+        <v>-4.8454</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8616</v>
+        <v>-3.2421</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9446</v>
+        <v>-1.6032</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4979</v>
+        <v>-5.2136</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4734</v>
+        <v>-1.5015</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0245</v>
+        <v>-3.7121</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-2.0177</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3531</v>
+        <v>-0.4384</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4414</v>
+        <v>-1.5793</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5861</v>
+        <v>-3.1959</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1203</v>
+        <v>-1.0631</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.4659</v>
+        <v>-2.1328</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9087</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0447</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1258</v>
+        <v>-0.0188</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8139</v>
+        <v>-0.0863</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3119</v>
+        <v>0.0675</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0913</v>
+        <v>0.387</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0913</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3027</v>
+        <v>-5.0159</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4849</v>
+        <v>-4.1494</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8178</v>
+        <v>-0.8665</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2756</v>
+        <v>0.2759</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6657</v>
+        <v>0.6662</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3901</v>
+        <v>-0.3903</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4559</v>
+        <v>1.4491</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2443</v>
+        <v>1.2411</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2117</v>
+        <v>0.2081</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1804</v>
+        <v>-1.1733</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5786</v>
+        <v>-0.5749</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6018</v>
+        <v>-0.5984</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.1806</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.534</v>
+        <v>-0.2415</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6247</v>
+        <v>-0.272</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0907</v>
+        <v>0.0305</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.8637</v>
+        <v>-1.8634</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.3767</v>
+        <v>-7.6183</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.8148</v>
+        <v>-3.9537</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.5619</v>
+        <v>-3.6646</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.3628</v>
+        <v>-1.3604</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.3727</v>
+        <v>-2.3722</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0099</v>
+        <v>1.0118</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9117</v>
+        <v>0.9036</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.9151</v>
+        <v>-0.921</v>
       </c>
       <c r="L26" t="n">
-        <v>1.8268</v>
+        <v>1.8246</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.2745</v>
+        <v>-2.264</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.4577</v>
+        <v>-1.4511</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8169</v>
+        <v>-0.8129</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.9534</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2133</v>
+        <v>-0.0302</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1828</v>
+        <v>-0.3046</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3961</v>
+        <v>0.2744</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.2738</v>
+        <v>-3.2684</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.2738</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-27.68389999999999</v>
+        <v>-27.6886</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.6367</v>
+        <v>-11.8344</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.0471</v>
+        <v>-15.854</v>
       </c>
       <c r="G27" t="n">
-        <v>-17.8981</v>
+        <v>-17.8885</v>
       </c>
       <c r="H27" t="n">
-        <v>1.315200000000001</v>
+        <v>1.295</v>
       </c>
       <c r="I27" t="n">
-        <v>-19.213</v>
+        <v>-19.1834</v>
       </c>
       <c r="J27" t="n">
-        <v>7.555399999999998</v>
+        <v>7.454899999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>9.2799</v>
+        <v>9.200899999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.7242</v>
+        <v>-1.7457</v>
       </c>
       <c r="M27" t="n">
-        <v>-25.4536</v>
+        <v>-25.3435</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.9647</v>
+        <v>-7.9054</v>
       </c>
       <c r="O27" t="n">
-        <v>-17.4887</v>
+        <v>-17.4377</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.2719</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q27" t="n">
-        <v>-19.3107</v>
+        <v>-19.3488</v>
       </c>
       <c r="R27" t="n">
-        <v>17.0389</v>
+        <v>17.0725</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.0823</v>
+        <v>-2.0912</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.658</v>
+        <v>-3.697</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5757</v>
+        <v>1.6062</v>
       </c>
       <c r="V27" t="n">
-        <v>-5.4317</v>
+        <v>-5.4323</v>
       </c>
       <c r="W27" t="n">
-        <v>3.7767</v>
+        <v>3.756699999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-9.208499999999999</v>
+        <v>-9.189200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104730_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104730_W31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-3.756699999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104730_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-9.189200000000001</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
